--- a/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0001T0006Z000C1N41_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0001T0006Z000C1N41_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>47.78102659414597</v>
+        <v>7.76441682154872</v>
       </c>
       <c r="D2" t="n">
-        <v>48.13451390609369</v>
+        <v>7.821858509740225</v>
       </c>
       <c r="E2" t="n">
-        <v>13.22885246096652</v>
+        <v>2.149688524907059</v>
       </c>
       <c r="F2" t="n">
-        <v>8.769794732305915</v>
+        <v>1.425091643999711</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>43.51496192096417</v>
+        <v>7.071181312156678</v>
       </c>
       <c r="D3" t="n">
-        <v>43.82741107495378</v>
+        <v>7.12195429967999</v>
       </c>
       <c r="E3" t="n">
-        <v>13.22885246096652</v>
+        <v>2.149688524907059</v>
       </c>
       <c r="F3" t="n">
-        <v>8.769794732305915</v>
+        <v>1.425091643999711</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>41.09582647616192</v>
+        <v>6.678071802376313</v>
       </c>
       <c r="D4" t="n">
-        <v>40.90934491721952</v>
+        <v>6.647768549048172</v>
       </c>
       <c r="E4" t="n">
-        <v>13.22885246096652</v>
+        <v>2.149688524907059</v>
       </c>
       <c r="F4" t="n">
-        <v>8.769794732305915</v>
+        <v>1.425091643999711</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>37.29554083557066</v>
+        <v>6.060525385780233</v>
       </c>
       <c r="D5" t="n">
-        <v>37.65209920397</v>
+        <v>6.118466120645125</v>
       </c>
       <c r="E5" t="n">
-        <v>13.22885246096652</v>
+        <v>2.149688524907059</v>
       </c>
       <c r="F5" t="n">
-        <v>8.769794732305915</v>
+        <v>1.425091643999711</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>33.00680154762135</v>
+        <v>5.36360525148847</v>
       </c>
       <c r="D6" t="n">
-        <v>32.78401078505306</v>
+        <v>5.327401752571123</v>
       </c>
       <c r="E6" t="n">
-        <v>13.22885246096652</v>
+        <v>2.149688524907059</v>
       </c>
       <c r="F6" t="n">
-        <v>8.769794732305915</v>
+        <v>1.425091643999711</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>57.99796082462465</v>
+        <v>9.424668634001506</v>
       </c>
       <c r="D7" t="n">
-        <v>29.30203063161871</v>
+        <v>4.76157997763804</v>
       </c>
       <c r="E7" t="n">
-        <v>13.22885246096652</v>
+        <v>2.149688524907059</v>
       </c>
       <c r="F7" t="n">
-        <v>8.769794732305915</v>
+        <v>1.425091643999711</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>12.10401931275025</v>
+        <v>1.966903138321916</v>
       </c>
       <c r="D8" t="n">
-        <v>20.25451020815552</v>
+        <v>3.291357908825272</v>
       </c>
       <c r="E8" t="n">
-        <v>13.22885246096652</v>
+        <v>2.149688524907059</v>
       </c>
       <c r="F8" t="n">
-        <v>8.769794732305915</v>
+        <v>1.425091643999711</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
